--- a/网络爬虫/text/新浪新闻.xlsx
+++ b/网络爬虫/text/新浪新闻.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新浪新闻" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -48,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,2122 +424,2722 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>简介</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>详情</t>
+          <t>链接</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>链接</t>
+          <t>来源</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>山东墨龙早盘涨逾17% 布伦特原油再站上100美元</t>
+          <t>范式智能午前涨逾3% 总价4亿元采购GPU服务器及相关配件</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>山东墨龙（00568）盘中涨超17%，截至发稿，股价上涨16.81%，现报9.35港元，成交额12.34亿港元。 4月23日早，国际油价短线冲高，WTI原油涨幅一度扩大至4%...</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>46135.46969907408</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>2026-04-30 11:33:44</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>范式智能（06682）盘中涨超3%，截至发稿，股价上涨2.84%，现报36.22港元，成交额1.87亿港元。 4月30日，范式智能发布公告，计划以总价4亿人民币购买GPU服务器及相关配件。...</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-30/doc-inhwfyep1358802.shtml</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-23/doc-inhvnaie5055799.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>快讯：能源化工期货涨幅持续扩大，低硫燃料油（LU）涨超7%</t>
+          <t>迈威生物-B早盘一度涨超23%创新高 公司已推动4款产品获批上市</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4月23日早盘，能源化工商品期货主力合约涨幅持续扩大，低硫燃料油（LU）涨超7%，燃料油涨超5%，SC原油涨超4%，对二甲苯涨超3%，PTA、瓶片涨超2%，苯乙烯、短纤、纯苯...</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>46135.46903935185</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>2026-04-30 11:31:40</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>迈威生物-B（02493）最高涨超23%，触及31.46港元，创上市新高。截至发稿，涨7.22%，报27.32港元，成交额1.84亿港元。 4月28日，迈威生物在港交所主板正式挂牌上市并首日入...</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/wm/2026-04-30/doc-inhwfyeh7154434.shtml</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvnaik5541882.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>龙蟠科技早盘涨超13% 公司锁定西澳Manna锂矿未来十年的稳定供货</t>
+          <t>全文|微软Q3业绩会实录：对与OpenAI整体合作结构满意</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>龙蟠科技（02465）盘中涨超17%，截至发稿，股价上涨13.67%，现报17.96港元，成交额9.28亿港元。 龙蟠科技与澳大利亚锂矿商GL1及其子公司GLR签下具有法律约束力的条款清单...</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>46135.46771990741</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>2026-04-30 11:26:59</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>微软公司今日公布了截至2026年3月31日的第三季度业绩。（注：微软财年与自然年不一致） 详见：微软营收同比增18% 利润同比增20% 云计算与AI驱动业绩增长 财报发布后...</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwfyeh7151539.shtml</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-23/doc-inhvnain3852943.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>亿腾嘉和早盘涨超3% 于2026年AACR年会公布四特异性抗体EDP001临床前研究数据</t>
+          <t>可孚医疗港股IPO：销售投入为研发投入13倍 净利润率长期徘徊10% 发行折扣35%仍缺吸引力</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>亿腾嘉和（06998）盘中涨近4%，截至发稿，股价上涨3.04%，现报3.39港元，成交额758.59万港元。 4月22日，据亿腾嘉和官微消息，公司宣布自主研发的具有高度创新性的四特异性...</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>46135.46633101852</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>2026-04-30 11:26:36</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>出品：新浪财经上市公司研究院 作者：喜乐 2026年4月27日，国内家用医疗器械企业可孚医疗正式启动港股招股，拟发行2700万股H股，发行价上限39.33港元/股...</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/observe/2026-04-30/doc-inhwfyef0374071.shtml</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-23/doc-inhvnain3851557.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>猪肉：入库与订单双增 4月屠企库存温和增多</t>
+          <t>先导智能午前涨超4% 第一季度归母净利润同比增长10.99%</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>卓创资讯肉类市场高级分析师马丽媛 【导语】伴随着上游猪源集中释放，2026年1月下旬至4月中旬，国内生猪及白条猪肉价格不断创历史新低。</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>46135.46503472222</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>2026-04-30 11:25:34</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>先导智能（00470）盘中涨超5%，截至发稿，股价上涨4.24%，现报58.95港元，成交额5325.05万港元。 近日，先导智能发布2026年第一季度业绩，营业收入约36.91亿元...</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/wm/2026-04-30/doc-inhwfyek6264315.shtml</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/2026-04-23/doc-inhvnaik5537944.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>纳芯微盘中涨超7% 模拟芯片巨头德州仪器一季度业绩超预期</t>
+          <t>独家|小红书发内部信：加大AI投入，柯南出任总裁</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>纳芯微（02676）盘中涨超7%，截至发稿，股价上涨2.82%，现报142.30港元，成交额5891.31万港元。 受益于数据中心和工业设备支出的激增，模拟芯片巨头德州仪器预计...</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>46135.46502314815</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>2026-04-30 11:25:29</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>新浪科技讯 4月30日上午消息，新浪科技独家获悉，4月30日，小红书发全员内部信，宣布新一轮组织升级，成立AI一级部门Dots和企业智能部，从产品技术...</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/chanjing/gsnews/2026-04-30/doc-inhwfyef0373287.shtml</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-23/doc-inhvnaie5051579.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>智谱盘中涨超9%再创上市新高 瑞银给予“买入”评级</t>
+          <t>天星医疗港股IPO：集采压力下毛利率逆升至74% 收入增速却腰斩 联创之一套现5亿离场</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>智谱（02513）盘中涨超9%，高见1078港元，再创上市新高。截至发稿，股价上涨3.96%，现报1025港元，成交额8.79亿港元。 智谱2026年一季度量价齐升...</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>46135.46452546296</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>2026-04-30 11:18:52</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>出品：新浪财经上市公司研究院 作者：喜乐 2026年4月24日，国内运动医疗器械公司天星医疗正式启动港股招股，发行价98.5港元/股，拟发行842.19万股，募资总额约8.3亿港元...</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/observe/2026-04-30/doc-inhwfyef0369422.shtml</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-23/doc-inhvnain3849788.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>东方甄选盘中涨超7% 公司正式切入高门槛的保健品行业</t>
+          <t>长安期货张晨：供给扰动频繁&amp;需求强劲释放，碳酸锂易涨难跌</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>东方甄选（01797）盘中涨超7%，截至发稿，股价上涨4.02%，现报28.98港元，成交额2.41亿港元。 近日，东方甄选在北京召开了一场保健食品发布会...</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>46135.46362268519</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>2026-04-30 11:18:05</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>一、行情走势回顾 碳酸锂期货价格强势突破18万元/吨关键关口，从技术面来看，价格此前形成收敛三角形整理形态，高点和低点同步收敛，振幅不断收窄...</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-30/doc-inhwfyeh7146172.shtml</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-23/doc-inhvnaik5536392.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>厄尔尼诺风险加剧，Czarnikow下调全球食糖过剩预估，糖价就要上涨了吗？</t>
+          <t>4月生猪均价环比下滑 5月均价或涨</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>云糖网yntw.com 2026年4月23日 在厄尔尼诺现象可能对主要产糖国收成造成冲击的背景下，国际知名糖业分析机构Czarnikow近日大幅下调了对2026/27年度全球食糖供需平衡的预测...</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>46135.46290509259</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>2026-04-30 11:15:33</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>卓创资讯生猪分析师 邹莹吉 【导语】4月生猪价格呈先降后涨走势，终端需求支撑偏弱，养殖端出栏节奏先快后慢、中后期压栏挺价。受生猪出栏量或将减少影响...</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-30/doc-inhwfyek6257584.shtml</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/2026-04-23/doc-inhvnaih8771893.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>油价上涨推升通胀预期压制降息空间，白银维持震荡调整</t>
+          <t>棕榈油：4月现货震荡走高</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>文章来源：汇通财经 周四亚洲时段，现货白银（XAG/USD）在前一交易日小幅反弹后再次走弱，价格回落至77.60美元/盎司附近，整体延续调整态势。</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>46135.45972222222</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>2026-04-30 11:14:11</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>卓创资讯棕榈油市场资深分析师张兰兰 【导语】4月棕榈油市场在多重因素交织下，呈现出明显震荡、多空博弈的复杂走势，价格在快速下探后强势反弹，最终维持高位震荡格局。</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-30/doc-inhwfyeh7143864.shtml</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/nmetal/hjzx/2026-04-23/doc-inhvnaie5047447.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>快讯：上期所燃油主力合约大涨5%，报4031元/吨</t>
+          <t>棉价加速上涨，下游纺企利润下降</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>北京时间4月23日，上期所燃油主力合约大涨5%，报4031元/吨。</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>46135.45881944444</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>2026-04-30 11:12:59</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>卓创资讯棉花市场资深分析师高飞堂 【导语】4月份棉花价格持续上涨，下游纺企生产成本不断增加，尤其下旬棉价上涨较快，纺企利润下降明显...</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-30/doc-inhwfyeh7143202.shtml</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvnaih8754310.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>“不只是司机的苦日子”——美高油价压力从运输业向消费端蔓延</t>
+          <t>特斯拉Semi卡车开始量产</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>新华社洛杉矶4月22日电 记者手记丨“不只是司机的苦日子”——美高油价压力从运输业向消费端蔓延 新华社记者高山 在美国加利福尼亚州洛杉矶市北部邻近5号州际高速的一处卡车服...</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>46135.45833333334</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>2026-04-30 11:10:05</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>特斯拉周三表示，其首辆Semi卡车已开始从大规模生产线上下线 。 “电动卡车Semi进入量产新阶段，”特斯拉在社交媒体平台上发文称。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwfyep1340266.shtml</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/jjxw/2026-04-23/doc-inhvnaik5536439.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>巨腾国际于4月23日上午起停牌 以待发布内幕消息</t>
+          <t>上半年钢铁产业链运行逻辑及未来关注点</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>巨腾国际（03336）公布，公司股份自2026年4月23日（星期四）上午九时正起于香港联合交易所有限公司短暂停止买卖，以待公司根据公司收购...</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>46135.44246527777</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>2026-04-30 11:06:32</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>（卓创资讯分析师邢月） 【导语】2026年以来，国内黑色系产品价格整体震荡偏强，个别品种有下调，呈现区间震荡走势，成本支撑叠加需求分化和供应减量材成为驱动价格变化的...</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-30/doc-inhwfyep1337263.shtml</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvnaik5516690.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>恒瑞医药绩后涨超5% 第一季度归母净利润同比增加21.78%</t>
+          <t>聚丙烯：2026年3月初级形状聚丙烯出口小析</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>恒瑞医药（01276）绩后涨超5%，截至发稿，股价上涨5.01%，现报70.20港元，成交额2.72亿港元。 4月22日，恒瑞医药发布公告，于2026年第一季度，该集团取得营业收入人民币81...</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>46135.44133101852</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>2026-04-30 11:03:39</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>卓创资讯聚丙烯分析师 薛铭慧 【导语】卓创资讯通过梳理海关数据，为您从出口贸易伙伴、贸易方式、成本区间及我国主要出口省份四个主要方面为您介绍2026年3月份我国出口聚...</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-30/doc-inhwfyep1334552.shtml</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-23/doc-inhvnain3821899.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>赛力斯盘中涨超6% 公司拟回购10亿至20亿元A股</t>
+          <t>广合科技绩后一度涨超10%创新高 第一季度净利润同比增长63.31%</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>赛力斯（09927）盘中涨超6%，截至发稿，股价上涨2.25%，现报81.85港元，成交额9020.80万港元。 赛力斯公告，公司拟通过集中竞价交易方式回购公司已经发行的人民币普通股（A...</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>46135.44027777778</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>2026-04-30 11:02:05</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 广合科技（01989）绩后一度涨超10%，高见195港元，创上市新高。截至发稿，涨幅收窄至上涨2.72%，现报181.40港元，成交额2.07亿港元。</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-30/doc-inhwfyeh7136786.shtml</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-23/doc-inhvnaie5021829.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H&amp;H国际控股盘中涨超7% 第一季度总收入按呈报基准按年上升34.4%</t>
+          <t>智谱盘中涨近5% 首次披露GLM-5超大规模Coding Agent推理工程实践</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H&amp;amp;H国际控股（01112）早盘一度涨超7%，截至发稿，股价上涨2.67%，现报14.16港元，成交额5792.34万港元。 4月22日，H&amp;amp;H国际控股发布公告...</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>46135.43914351852</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>2026-04-30 10:59:21</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>智谱（02513）盘中涨近5%，截至发稿，股价上涨4.35%，报852港元，成交额6.48亿港元。 4月30日，智谱公众号发文，首次系统披露GLM-5系列模型在超大规模Coding...</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-30/doc-inhwfyef0358119.shtml</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-23/doc-inhvnain3818785.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>农业农村部：生猪供求关系逐步改善 价格企稳</t>
+          <t>新华保险早盘涨超3% 市场波动态势下利润超预期增长10.5%</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>人民财讯4月23日电，国新办就2026年一季度农业农村经济运行情况举行新闻发布会。农业农村部副部长麦尔丹·木盖提介绍一季度农业农村经济运行情况，“菜篮子”产品供应充足。</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>46135.43680555555</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>2026-04-30 10:57:14</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>新华保险（01336）绩后曾涨超4%，截至发稿，股价上涨3.06%，现报52.15港元，成交额4.96亿港元。 新华保险发布一季报，期内营业收入221.33亿元，同比下滑33...</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/wm/2026-04-30/doc-inhwfyef0356934.shtml</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/jjxw/2026-04-23/doc-inhvnaie5018799.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>新西兰财长称经济复苏延缓 但并未脱离轨道</t>
+          <t>金风科技早盘涨逾3% 拟回购不超过5亿元A股股份</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 新西兰财政部长Nicola Willis周四表示，新西兰刚刚起步的经济复苏因伊朗战争而受到影响，但预计仍将在今年晚些时候重回正轨。</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>46135.43409722222</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>2026-04-30 10:54:14</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>金风科技（02208）盘中涨超3%，截至发稿，股价上涨2.84%，现报17.03港元，成交额2.67亿港元。 4月29日，金风科技发布公告，本公司拟使用自有资金以集中竞价交易的方式回购...</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-30/doc-inhwfyeh7132511.shtml</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvnain3812135.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>美国海军部长费伦据悉因与五角大楼高层发生冲突而被解职</t>
+          <t>信达生物早盘涨逾5% 第一季度产品收入同比增长超过50%</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 据知情人士称，美国海军部长约翰·费伦在与五角大楼高层发生冲突后被解职，争执焦点包括特朗普政府重振美国造船业的计划。</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>46135.4308912037</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>2026-04-30 10:52:31</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>信达生物（01801）早盘涨逾5%，截至发稿，股价上涨4.95%，现报89.10港元，成交额7.49亿港元。 4月30日，信达生物发布公告，于2026年第一季度...</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/wm/2026-04-30/doc-inhwfyek6239071.shtml</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvnain3807288.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>国民技术早盘涨超10% 发布N32H493主控芯片适配800G/1.6T光模块</t>
+          <t>亚马逊探讨重启真人秀节目《学徒》，小特朗普或任主持人</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>国民技术（02701）早盘涨超10%，截至发稿，股价上涨10.25%，现报13.77港元，成交额3.78亿港元。 近日，国民技术通过官方公众号正式发布面向800G/1...</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>46135.43047453704</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>2026-04-30 10:35:16</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 继买下纪录片《梅拉尼娅》之后，亚马逊目前正探讨重启真人秀节目《学徒》（The Apprentice）。现任美国总统唐纳德．特朗普曾是该节目的明星，并借此名扬全美。</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwftwr1441241.shtml</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-23/doc-inhvnain3806719.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>康耐特光学盘中涨超4% 已与一家智能眼镜领域头部企业签署合作备忘录</t>
+          <t>上海石化绩后涨逾4% 第一季度归母净利润约4.15亿元同比扭亏为盈</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>康耐特光学（02276）早盘涨超4%，截至发稿，股价上涨3.04%，现报50.80港元，成交额1.42亿港元。 4月22日，康耐特光学发布公告，公司在智能眼镜光学解决方案领域迎来里程碑...</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>46135.42650462963</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>2026-04-30 10:32:31</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>上海石化（00338）绩后涨逾4%，截至发稿，股价上涨3.97%，现报1.31港元，成交额3687.99万港元。 4月29日，上海石化发布公告，于2026年第一季度，营业收入约176.62亿元...</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-30/doc-inhwftwn6351655.shtml</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-23/doc-inhvnaik5503452.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>长江有色：硫酸短缺令全球铜企承压 23日铜价或大涨</t>
+          <t>特朗普要降息，同僚却反对：沃什的美联储主席之路开局即地狱模式</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 长江铜价copper.ccmn.cn短评：特朗普意外同意延长与伊停火协议改善风险情绪且伦铜库存下降，隔夜伦铜涨2.4%；硫酸短缺令全球铜企承压，国内旺季消费尚可，今现铜或大涨。</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>46135.42351851852</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>2026-04-30 10:30:39</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>随着凯文·沃什距离出任美联储主席越来越近，他未来的同僚们却与特朗普所期待的恢复降息渐行渐远。 在现任主席杰罗姆·鲍威尔主持的最后一次会议上...</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/hkstocknews/2026-04-30/doc-inhwfyef0346296.shtml</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/indu/2026-04-23/doc-inhvmvzh5131311.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>长江有色：美伊停火与对峙并存+矿紧锭松格局延续 23日锌价或上涨</t>
+          <t>锂矿概念股早盘上涨 天齐锂业上涨3.64%赣锋锂业上涨1.01%</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 【ccmn.cn摘要】美股全线走强且市场对和平协议存预期，隔夜伦锌涨0.86%创逾三年新高；海外矿紧、柴油紧张致冶炼额外减产，LME库存低位，今现锌或跟涨。</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>46135.42344907407</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>2026-04-30 10:30:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 锂矿概念股早盘上涨，天齐锂业（09696）上涨3.64%，报65.55港元；截至发稿，赣锋锂业（01772）上涨1.01%，报84.80港元。</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-30/doc-inhwftwk7247353.shtml</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/indu/2026-04-23/doc-inhvmvzn5631671.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>长江有色：美伊和谈生变及AI 半导体狂欢提振 23日锡价或上涨</t>
+          <t>三花智控绩后涨逾5% 第一季度归母净利润9.28亿元同比增加2.68%</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>期货市场：美股全线走强AI 半导体狂欢引爆 “算力金属”，隔夜伦锡收涨2%；最新收盘报50595美元/吨，上涨990美元，涨幅为2%，成交量为282手，持仓量21187万手；国内方面...</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>46135.42344907407</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>2026-04-30 10:28:31</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>三花智控（02050）绩后涨逾5%，截至发稿，股价上涨4.89%，现报33.44港元，成交额3.66亿港元。 4月29日，三花智控发布2026年第一季度报告，该公司取得营业收入77.74亿元...</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/wm/2026-04-30/doc-inhwftwr1435159.shtml</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/indu/2026-04-23/doc-inhvmvzq3929697.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>长江有色：产业链分化铅价窄幅震荡 23日铅价或涨跌不大</t>
+          <t>华泰期货：行业景气度较高，碳酸锂近日价格强势运行</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 【ccmn.cn铅期货市场】隔夜伦铅收涨，开盘报1963.50美元/吨，高点报1970美元，低点报1951美元，尾盘收于1963.50美元，上涨6美元，成交量为7039手，持仓量报180506手。</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="n">
-        <v>46135.42341435186</v>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>2026-04-30 10:24:11</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>来源：华泰期货 作者： 新能源及有色组 昨日碳酸锂盘面增仓上涨，主力合约2609增仓26021手，涨幅3.73%，收盘上涨至183880元/吨，目前总合约持仓量47.91万手...</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-30/doc-inhwftwi0465629.shtml</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/indu/2026-04-23/doc-inhvmvzq3929603.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>长江有色:  地缘黑天鹅至国际铝短缺与国内过剩的博弈 23日铝价或上涨</t>
+          <t>华泰期货：油价强势上涨，沥青成本端支撑坚挺</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 长江铝价alu.ccmn.cn短评：供应端“黑天鹅”事件持续冲击全球铝市，隔夜伦铝领涨2.58%；国内银色消费不佳、社库累至高位，但海湾通航存疑、国际原铝有缺口，今现铝或上涨。</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>46135.42340277778</v>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>2026-04-30 10:21:05</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>来源：华泰期货 作者： 康远宁 市场分析 1、4月29日沥青期货下午盘收盘行情：主力BU2606合约下午收盘价4409元/吨，较昨日结算价上涨60元/吨；持仓218582手...</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-30/doc-inhwftwk7240509.shtml</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/indu/2026-04-23/doc-inhvmvzq3930859.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>长江有色：美伊停火期望及印尼政策托底 23日镍价或小涨</t>
+          <t>摩根资产管理认为美联储加息的门槛很高</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>镍期货市场：中东局势边际缓和全球风险偏好显著回升，隔夜伦镍收涨1.74%；伦镍最新收盘报18465，比前一交易日上涨315美元/吨，涨幅为1.74%，成交量6449手，国内市场...</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>46135.42336805556</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>2026-04-30 10:18:35</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>摩根资产管理亚太首席市场策略师Tai Hui表示，美联储在可预见的未来可能维持利率不变。 Tai Hui表示，鉴于多数委员觉得当前政策立场已属于中性，美联储可以保持耐心...</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwftwr1426201.shtml</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/indu/2026-04-23/doc-inhvmvzq3929353.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ASMPT盘中涨超7% 首季盈利及第二季展望均超预期</t>
+          <t>华泰期货：供应端矛盾持续积累，燃料油市场结构支撑偏强</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ASMPT（00522）盘中涨超7%，截至发稿，股价上涨5.06%，现报159.90港元，成交额3.19亿港元。 ASMPT近日公布一季度财报，持续经营业务销售收入达39.7亿港元，同比增长32...</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>46135.42087962963</v>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>2026-04-30 10:12:46</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>来源：华泰期货 作者： 康远宁 市场分析 上期所燃料油期货主力合约夜盘收涨3.38%，报4460元/吨；INE低硫燃料油期货主力合约夜盘收涨4.16%，报5080元/吨。</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-30/doc-inhwftwn6334897.shtml</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-23/doc-inhvmvzh5127117.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>中信建投期货：4月23日能化早报</t>
+          <t>华泰期货：苹果增产预期压制，红枣去库缓慢</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PX： 供需面供需双减。亚洲行业负荷环比减少3.3pct至66.5%，中国PX行业负荷环比减少1.7pct至80.2%，随 着封锁前最后一批海上货源到港...</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>46135.41122685185</v>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>2026-04-30 10:07:13</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>来源：华泰期货 作者： 白旭宇 苹果观点 市场要闻与重要数据 期货方面，昨日收盘苹果2610合约7615元/吨，较前一日变动+62元/吨，幅度+0.82%。</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-30/doc-inhwftwk7229347.shtml</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzk8841530.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>中信建投期货：4月23日农产品早报</t>
+          <t>华泰期货：黑色板块回调，双焦震荡偏弱</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>玉米：中性 1．市场关注：此前市场普遍担忧4月启动的2000万吨定向稻谷投放至今迟迟未落地，供给端预期差为多头提供了重要支撑，同时现货端报价大涨...</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>46135.41065972222</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>2026-04-30 10:02:51</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>市场分析 期现货方面：昨日双焦期货震荡偏弱运行，坑口煤价稳中上涨，焦炭提涨迟迟不见落地，蒙5原煤报价在1120-1130元/吨左右，报还盘差价较大，口岸成交相对清淡。</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-30/doc-inhwftwr1413150.shtml</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzh5114321.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>中信建投期货：4月23日工业品早报</t>
+          <t>埃斯顿盘中涨超7% 第一季度净利润同比大增逾6.7倍</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>铜：基本面强化，铜价偏强震荡 周三晚沪铜量价齐增，主力合约涨1.4%至10.39万元，伦铜上行至13480美金附近。 宏观中性。特朗普称最快周五可能重启美伊谈判...</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>46135.41024305556</v>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>2026-04-30 10:01:13</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>埃斯顿（02715）早盘一度涨超7%，截至发稿，股价上涨4.92%，现报13港元，成交额2250.46万港元。 埃斯顿发布2026年第一季度报告，该集团取得营业收入12.17亿元，同比减少2...</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-30/doc-inhwftwn6324680.shtml</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzk8840532.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>日本以国家安全风险为由 反对韩国MBK Partners收购牧野铣床</t>
+          <t>中国中车绩后涨超4% 第一季度归母净利润同比增加10.66%</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 牧野铣床株式会社表示，日本政府出于国家安全担忧，已要求总部位于首尔的私募股权公司MBK Partners取消对该公司的收购计划。</t>
-        </is>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>46135.40975694444</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>2026-04-30 09:59:30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>中国中车（01766）绩后涨超4%，截至发稿，股价上涨3.31%，现报5.31港元，成交额4529.09万港元。 4月29日，中国中车发布2026年第一季度业绩，该集团取得营业收入538...</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/wm/2026-04-30/doc-inhwftwr1410178.shtml</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzh5113143.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>中信建投期货：4月23日黑色系早报</t>
+          <t>白宫反对Anthropic扩大Mythos模型使用范围的计划</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>钢材早报：成本支撑较强，期钢震荡偏强运行 市场信息： 1、 美国总统特朗普表示，美伊新一轮和平谈判“最早可能在周五”取得进展。</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>46135.40887731482</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>2026-04-30 09:57:25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 白宫反对Anthropic扩大其人工智能（AI）模型Mythos使用范围的计划，这使得这款能够发动网络攻击并造成大范围网络混乱的AI工具的推广变得复杂。</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwftwi0444191.shtml</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzn5616393.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>华勤技术首挂上市 早盘高开13.13%公司为全栈智能产品ODM平台</t>
+          <t>潍柴动力绩后涨逾9% 第一季度归母净利润同比增长13.83%</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>华勤技术（03296）首挂上市，公告显示，每股定价77.7港元，共发行5854.82万股股份，每手100股，所得款项净额约44.63亿港元。截至发稿，股价上涨13.13%，现报87.90港元...</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46135.40274305556</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>2026-04-30 09:48:13</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>潍柴动力（02338）绩后上涨逾9%，截至发稿，股价上涨8.25%，现报39.10港元，成交额2.56亿港元。 4月29日，潍柴动力发布公告，2026年第一季度，营业收入625.63亿元...</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-30/doc-inhwftwn6312118.shtml</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggipo/2026-04-23/doc-inhvmvzn5609422.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>光大期货：4月23日农产品日报</t>
+          <t>中信建投证券早盘涨逾8% 第一季度营业收入同比增加62.26%</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>蛋白粕： （侯雪玲，从业资格号：F3048706；交易咨询资格号：Z0013637） 周三，CBOT大豆下跌，受累于获利了结和技术性抛售，美豆粕和美豆油价格跟随走低。</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46135.40222222222</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>2026-04-30 09:45:57</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>中信建投证券（06066）盘初涨超8%，截至发稿，股价上涨7.80%，现报12.03港元，成交额9335.19万港元。 中信建投证券公布，于2026年第一季度，该集团取得营业收入76.96亿元...</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/wm/2026-04-30/doc-inhwftwi0437716.shtml</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzh5102975.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>存储概念早盘集体高开 澜起科技涨超8%兆易创新涨超5%</t>
+          <t>广深铁路股份绩后涨超4% 第一季度归母净利润同比增加23.8%</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>存储概念早盘集体高开，截至发稿，南方两倍做多三星电子（07747）上涨9.01%，报97.02港元；澜起科技（06809）上涨8.02%，报242.40港元；兆易创新（03986）上涨5.56%...</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46135.40136574074</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>2026-04-30 09:43:26</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>广深铁路股份（00525）绩后涨超4%，截至发稿，股价上涨3.40%，现报2.43港元，成交额998.91万港元。 4月29日，广深铁路股份发布2026年第一季度报告...</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-30/doc-inhwftwi0436218.shtml</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-23/doc-inhvmvzh5101769.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>摩根大通对智谱、MiniMax维持超配 关注竞争格局与商业变现的不确定性</t>
+          <t>中国人寿绩后涨超5% 第一季度新业务价值同比增长75.5%</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 摩根大通发表报告称，中国AI初创企业智谱与MiniMax自年初IPO以来股价大涨，仍维持对两家公司的建设性看法与“超配”评级，技术性因素驱动的回调是良好的买入机会。</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="n">
-        <v>46135.40119212963</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>2026-04-30 09:41:24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>中国人寿（02628）绩后涨超5%，截至发稿，股价上涨5.18%，现报28.82港元，成交额6.27亿港元。 中国人寿发布一季度业绩，营业收入为932.91亿元，同比减少15...</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/wm/2026-04-30/doc-inhwftwi0435129.shtml</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzn5607262.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>光大期货：4月23日软商品日报</t>
+          <t>长江有色：美联储鹰派风暴美指走强施压 30日锡价或下跌</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>白糖： （张笑金，从业资格号：F0306200；交易咨询资格号：Z0000082） 现货报价方面，广西制糖集团报价区间为5320~5410元/吨，上调20~30元/吨；云南制糖集团报价5150~...</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>46135.40091435185</v>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>2026-04-30 09:40:39</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>期货市场：美联储鹰派风暴美股震荡走弱，隔夜伦锡收跌0.73%；最新收盘报48745美元/吨，下跌360美元，跌幅为0.73%，成交量为815手，持仓量20968万手；国内方面...</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/indu/2026-04-30/doc-inhwftwn6302641.shtml</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzk8829637.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>微软承诺投资180亿美元拓展澳大利亚AI市场</t>
+          <t>去世12年父亲信用卡欠款滚到2.3万 这笔钱该不该还？</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 微软宣布对澳大利亚进行有史以来最大的一笔投资，承诺到2029年底投资250亿澳元（179亿美元），以进一步拓展在亚太地区的人工智能市场。</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>46135.40070601852</v>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>2026-04-30 09:38:56</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>近日，上海市民陶女士被银行催还父亲信用卡欠债的经历引发媒体的关注，陶女士的父亲2014年就因病去世了，她当年主动还清父亲所有信用卡欠款。</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/jjxw/2026-04-30/doc-inhwftwr1395358.shtml</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzh5100751.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>光大期货：4月23日有色金属日报</t>
+          <t>油价若长期高居不下 或加剧新兴市场亚洲债券的抛售</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>铜： （展大鹏，从业资格号：F3013795；交易咨询资格号：Z0013582） 隔夜内外铜价震荡走高，国内精炼铜现货进口维持小幅盈利。宏观方面...</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>46135.40020833333</v>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>2026-04-30 09:37:15</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 如果以史为鉴，油价长期处于高位可能会使亚洲新兴市场债券收益率加快上升。市场观察人士表示，这种风险尚未被充分反映在市场价格中。</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwftwn6297922.shtml</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzn5605893.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>华泰期货：政策利好刺激市场情绪，多晶硅价格持续上涨</t>
+          <t>晓数点｜美联储迎1992年以来最分裂表决，特朗普掌控理事会梦想破灭</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>来源：华泰期货 作者： 师橙 市场分析 2026-04-22日，多晶硅期货主力合约2606震荡上涨，开于42550元/吨，最后收于45300元/吨，收盘价较上一交易日变化5.13%。</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="n">
-        <v>46135.40019675926</v>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>2026-04-30 09:31:14</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>一图速览&amp;gt;&amp;gt;</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/roll/2026-04-30/doc-inhwftwk7206606.shtml</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzq3898634.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>锅圈早盘高开逾6% 拟公开回购不低于2亿港元H股</t>
+          <t>OpenAI提前数年实现关键AI算力目标</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>锅圈（02517）早盘高开逾6%，截至发稿，股价上涨6.23%，现报3.24港元，成交额1770.32万港元。 锅圈发布公告，2026年4月22日，董事会作出决议...</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="n">
-        <v>46135.3996412037</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>2026-04-30 09:27:42</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>OpenAI提前数年实现在美国获取人工智能（AI）算力的关键里程碑，为这家初创公司雄心勃勃的数据中心扩张计划注入动力。 该公司周三在一篇博客文章中称...</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwftwi0423085.shtml</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-23/doc-inhvmvzq3897772.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>华泰期货：俄罗斯4月燃料油出口预计出现下滑</t>
+          <t>黄河实业于4月30日上午起短暂停牌</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>来源：华泰期货 作者： 康远宁 市场分析 上期所燃料油期货主力合约夜盘收涨2.7%，报3874元/吨；INE低硫燃料油期货主力合约夜盘收涨2.51%，报4459元/吨。</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="n">
-        <v>46135.39865740741</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>2026-04-30 09:23:46</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>黄河实业（00318）发布公告，该公司股份将于今天（30/4/2026）上午九时正起短暂停止买卖。</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/wm/2026-04-30/doc-inhwftwe7484071.shtml</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzq3896040.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>光大期货：4月23日金融日报</t>
+          <t>钉钉陈航：AI招聘看AIQ，学历经历年龄不再重要</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>股指： （王东灜，从业资格号：F03087149；交易咨询资格号：Z0019537） 昨日，全球股指市场多数收涨，日韩股指涨幅明显。Wind全A上涨0.96%，成交额2.58万亿元。</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="n">
-        <v>46135.39776620371</v>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>2026-04-30 09:23:36</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>新浪科技讯 4月30日上午消息，阿里巴巴钉钉/悟空创始人、CEO陈航近日在2026清华五道口（浙江）金融发展论坛分享了一个特别的观点：未来企业的核心指标不再是KPI与OKR...</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/tech/2026-04-30/doc-inhwftwi0419995.shtml</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzq3894474.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>华泰期货：供应偏高背景延续，生猪市场情绪呈现好转</t>
+          <t>快讯：恒指低开0.40% 科指跌0.68% 科网股普跌 半导体股活跃</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>来源：华泰期货 作者： 薛钧元 生猪观点 市场要闻与重要数据 期货方面，昨日收盘生猪 2607合约11410元/吨，较前交易日变动+295.00元/吨，幅度+2.65%。</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="n">
-        <v>46135.39768518518</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>2026-04-30 09:20:46</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>美股周三个变发展，油价持续高企，打击大市气氛，联储局一如预期维持息率不变，对市场未有太大影响，三大指数收市升跌不一。美元走势向好，美国十年期债息上升至4...</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-30/doc-inhwftwk7196918.shtml</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzq3894336.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>华泰期货：轮胎厂原料补库，支撑橡胶现货价格</t>
+          <t>全文|谷歌Q1业绩会实录：智能代理将重塑购物体验 将向客户提供TPU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>来源：华泰期货 作者： 陈莉 市场要闻与数据 期货方面，昨日收盘RU主力合约17065元/吨，较前一日变动-15元/吨；NR主力合约14105元/吨...</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="n">
-        <v>46135.39586805556</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>2026-04-30 09:17:59</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>谷歌母公司Alphabet今日公布了截至2026年3月31日的第一季度财务业绩。 详见：Alphabet营收同比增长22% 净利润同比增长81% 云业务加速增长 财报发布后...</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwftwi0415547.shtml</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzq3891279.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>光大期货：4月23日矿钢煤焦日报</t>
+          <t>中信建投期货：4月30日黑色系早报</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>螺纹钢： （邱跃成，从业资格号：F3060829；交易咨询资格号：Z0016941） 昨日螺纹盘面偏强震荡，截止日盘螺纹2610合约收盘价格为3186元/吨...</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="n">
-        <v>46135.39547453704</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>2026-04-30 09:15:47</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>钢材早报：期钢高位震荡，关注终端成交持续性 市场信息： 1、 美联储公布4月议息决议，以8：4的罕见投票结果维持联邦基金利率目标区间于3.50%–3.75%不变...</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/2026-04-30/doc-inhwftwe7474811.shtml</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzh5092111.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>光大期货：4月23日能源化工日报</t>
+          <t>【市场聚焦】五一假期风险提示</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>原油： （钟美燕，从业资格号：F3045334；交易咨询资格号：Z0002410） 周三油价上涨，其中WTI 新换6月合约收盘上涨3.29美元至92.96美元/桶，涨幅3.67%。</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="n">
-        <v>46135.39443287037</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>2026-04-30 09:15:14</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>中粮期货研究中心 观点概览 金属新材料板块 化工品板块 农产品板块 黑色板块 数据来源：wind，中粮期货研究院整理  正文 1、宏观 当前全球市场处于高波动、高预期...</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/2026-04-30/doc-inhwftwe7480164.shtml</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzh5090769.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>原油交易提醒：地缘局势反复叠加库存下降，油价冲高回落，维持高位震荡</t>
+          <t>LG新能源一季度营业亏损2080亿韩元，因北美电动汽车需求疲软</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>文章来源：汇通财经 周四亚洲交易时段，WTI原油价格在触及阶段高点后出现回落，盘中一度升至97.20美元附近，创近一周半新高，但随后回吐部分涨幅，目前维持在93美元上方...</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="n">
-        <v>46135.39236111111</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>2026-04-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>韩国LG新能源公司周四报告第一季度业绩由盈转亏，因电动汽车制造商的电池需求疲软，尤其是北美地区的客户。 LG新能源公司是特斯拉、通用汽车和现代汽车的电池供应商...</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwftwi0412796.shtml</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzh5090097.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Swift数据显示 美元3月份在国际交易中占比升至51.1%的新高</t>
+          <t>全文|Meta Q1业绩会实录：智能眼镜需求强劲 OpenClaw太难用</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>根据环球银行金融电信协会（Swift）最新汇编的数据，美元在3月份国际交易中的比例升至创纪录的51.1%，高于一个月前的49.2%。这也创下自2023年以来的最高...</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="n">
-        <v>46135.39212962963</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>2026-04-30 09:14:36</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Meta Platforms今日公布了截至2026年3月31日的第一季度财务业绩。 详见：Meta营收增长33% 净利润增长61% 上调全年资本支出预期 财报发布后...</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwftwi0412381.shtml</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzn5597780.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>快讯：恒指低开0.25% 科指跌0.04% 科网股低迷 芯片股高开</t>
+          <t>中信建投期货：4月30日工业品早报</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>美股周三表现向好，美国总统特朗普宣布延长美伊的停火，刺激大市造好，纳指及标普500指数再创收市新高，三大指数均录得升幅收市。</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="n">
-        <v>46135.38902777778</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>2026-04-30 09:14:36</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>铜：节前情绪降温，铜价延续承压 隔夜沪铜主力走软至100820元，伦铜收阴倒锤子线至1.3万美金下沿。 宏观中性。美联储维持当前利率按兵不动...</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/2026-04-30/doc-inhwftwk7189604.shtml</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/marketalerts/2026-04-23/doc-inhvmvzk8818939.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>软银据悉寻求抵押OpenAI股份贷款100亿美元</t>
+          <t>中信建投期货：4月30日农产品早报</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>据知情人士，软银集团正以其持有的ChatGPT开发商OpenAI的股份作为抵押，寻求一笔100亿美元的贷款。 消息人士称，这笔为期两年的保证金贷款将包含软银可选择将借款期限延长...</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="n">
-        <v>46135.38478009259</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>2026-04-30 09:13:27</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>玉米：中性 1．市场关注：产区流通量偏少而销区需求平淡，玉米现货整体维持横盘整理，多空双方暂无明显支撑。短期政策收储边际减弱、新麦上市预期...</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/2026-04-30/doc-inhwftwi0411305.shtml</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzq3875151.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>快讯：生猪主力合约延续走高，日内涨超2.00%，现报11545.00元/吨</t>
+          <t>中信建投期货：4月30日能化早报</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>生猪主力合约延续走高，日内涨超2.00%，现报11545.00元/吨。</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="n">
-        <v>46135.38190972222</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>2026-04-30 09:12:12</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>橡胶：再度冲高回落 周三，国产全乳胶17450/吨，环比上涨200元/吨；泰国20号混合胶16900元/吨，环比上日上涨250元/吨。 原料端：泰国胶水报收80.75泰铢/公斤...</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/2026-04-30/doc-inhwftwk7187305.shtml</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzn5587471.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>软银据悉寻求以OpenAI股份作抵押 获得100亿美元保证金贷款</t>
+          <t>光大期货：4月30日软商品日报</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 知情人士称，软银集团正寻求一笔100亿美元的贷款，以所持美国人工智能（AI）巨头OpenAI的股份作抵押。因大力进军AI领域，这家日本企业集团正背上更多债务。</t>
-        </is>
-      </c>
-      <c r="C55" s="1" t="n">
-        <v>46135.37686342592</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>2026-04-30 09:10:29</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>白糖： （张笑金，从业资格号：F0306200；交易咨询资格号：Z0000082） 消息方面，巴西国家商品供应公司（Conab）发布首期2026/27榨季甘蔗调查报告...</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/2026-04-30/doc-inhwftwe7470696.shtml</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzk8804888.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>开盘：国内期货主力合约涨多跌少 多晶硅涨超2%</t>
+          <t>光大期货：4月30日有色金属日报</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 4月23日早盘开盘，国内期货主力合约涨多跌少。多晶硅、20号胶涨超2%，低硫燃油、香蕉、燃油、沪铜、玻璃、生猪涨超1%；苹果、豆粕、玉米淀粉小幅下跌。</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="n">
-        <v>46135.37615740741</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>2026-04-30 09:09:50</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>铜： （展大鹏，从业资格号：F3013795；交易咨询资格号：Z0013582） 隔夜内外铜价震荡走弱，国内现货精炼铜进口小幅盈利。宏观方面，地缘政治方面...</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/2026-04-30/doc-inhwftwn6269472.shtml</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzn5581149.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>中播数据公布于4月23日上午起复牌</t>
+          <t>光大期货：4月30日金融日报</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>中播数据（00471）公布，公司股份自2026年4月23日上午9点起复牌。</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="n">
-        <v>46135.37328703704</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>2026-04-30 09:09:13</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>股指： （王东灜，从业资格号：F03087149；交易咨询资格号：Z0019537） 昨日，全球股指多数收跌，Wind全A上涨1.33%，成交额2.61万亿元。</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/2026-04-30/doc-inhwftwe7469966.shtml</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmvzq3862958.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>日经指数首次升破60000点</t>
+          <t>光大期货：4月30日矿钢煤焦日报</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>在日本芯片相关股上涨的带动下，该国日经指数首次短暂升破60000点大关，与此同时，市场对美伊冲突的谨慎情绪持续。日经指数现上涨0.5%，报59，865.70点，早盘一度上涨0...</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="n">
-        <v>46135.37284722222</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>2026-04-30 09:08:23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>螺纹钢： （邱跃成，从业资格号：F3060829；交易咨询资格号：Z0016941） 昨日螺纹盘面有所反弹，截止日盘螺纹2610合约收盘价格为3195元/吨...</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/2026-04-30/doc-inhwftwk7183824.shtml</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzh5064019.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>高雅光学公布于4月23日上午起停牌</t>
+          <t>光大期货：4月30日能源化工日报</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>高雅光学（00907）公布，于2026年4月22日，公司接获上市复核委员会的函件，通知经考虑公司及上市科提交的意见书（包括公司在聆讯时提交的意见书）后...</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="n">
-        <v>46135.37260416667</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>2026-04-30 09:07:49</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>原油： （钟美燕，从业资格号：F3045334；交易咨询资格号：Z0002410） 周三油价重心再度大幅上涨，其中WTI 6月合约收盘上涨6.95美元至106.88美元/桶，涨幅6.96%。</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/2026-04-30/doc-inhwftwn6268193.shtml</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmvzq3862535.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>大摩：复星医药给予“增持”评级 目标价32港元</t>
+          <t>软银据报计划在美国成立并上市AI公司Roze 目标估值1000亿美元</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>摩根士丹利发布研报称，将复星医药（02196）2026至2028年收入预测上调3%，基于创新药销售额上升，以及预期每年入账约8亿元人民币的经常性授权收入。</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="n">
-        <v>46135.37116898148</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>2026-04-30 09:07:31</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>媒体援引未具名知情人士的消息报道，软银集团计划在美国成立并上市一家名为Roze的独立AI机器人和数据中心公司。 报道称，这家日本投资公司计划最快今年让Roze上市...</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwftwk7183046.shtml</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/hkgg/2026-04-23/doc-inhvmvzn5577753.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>里昂：福耀玻璃料可实现盈利持续增长 维持“跑赢大市”评级</t>
+          <t>光大期货：4月30日农产品日报</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>里昂发布研报称，福耀玻璃（03606）公布2026财年首季业绩，净利润下跌15.7%，受累于4.39亿元人民币的外汇损失。撇除外汇影响，经营净利润同比增20%。</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="n">
-        <v>46135.37114583333</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>2026-04-30 09:06:59</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>蛋白粕： （侯雪玲，从业资格号：F3048706；交易咨询资格号：Z0013637） 周三，CBOT大豆上涨，受伊朗局势引发的原油上涨提振。此外，美豆压榨利润改善也带动市场走高。</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/2026-04-30/doc-inhwftwk7182567.shtml</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/hkgg/2026-04-23/doc-inhvmvzk8800531.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>中信证券：五一视界首予“增持”评级 目标价68港元</t>
+          <t>文化传信拟折让约15.08%配售合共6541.9万股认购股份 净筹约689万港元</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>随着人工智能从数字世界迈向物理世界，数字孪生正成为连接虚拟与现实的底层基础设施。在这一赛道上，五一视界（06651）正以“3D+仿真+AI”的全栈能力...</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="n">
-        <v>46135.37112268519</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>2026-04-30 09:06:38</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>文化传信（00343）发布公告，于2026年4月29日（交易时段后），本公司与认购人订立认购协议，据此，本公司有条件同意配发及发行，而认购人有条件同意以每股认购股份0...</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-30/doc-inhwftwn6267316.shtml</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/wm/2026-04-23/doc-inhvmvzn5577728.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>力天影业完成发行6800万股配售股份</t>
+          <t>农业农村部成立生猪产业监测预警专家咨询委员会</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>力天影业（09958）发布公告，配售协议所载之所有条件已获达成，而配售事项已于2026年4月22日完成。合共6800万股配售股份（占公司经紧随完成后配发及发行配售股份扩大后已发...</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="n">
-        <v>46135.37108796297</v>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>2026-04-30 09:06:00</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>转自：农业农村部网站 本网讯4月28日，农业农村部召开生猪产业监测预警专家咨询委员会成立大会，深入学习贯彻习近平总书记重要指示精神，认真落实党中央、国务院决策部署...</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/jjxw/2026-04-30/doc-inhwftwi0425005.shtml</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/hkgg/2026-04-23/doc-inhvmvzn5577713.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>灵宝黄金完成配售现有股份及根据一般授权先旧后新认购新股份</t>
+          <t>华勤技术拟派发末期股息每10股12元</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>灵宝黄金（03330）发布公告，配售事项已根据配售及认购协议的条款及条件于2026年4月16日完成。其中，配售股份（合共2981.6万股H股）已由配售代理按尽力基准...</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>46135.37105324074</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>2026-04-30 09:04:02</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>华勤技术（03296）发布公告，该公司拟派发末期股息每10股12元。</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/wm/2026-04-30/doc-inhwftwn6265175.shtml</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmvzn5577682.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ECI TECH发布中期业绩 股东应占溢利657万港元同比增加44.65%</t>
+          <t>开盘|国内期货主力合约涨多跌少 低硫燃料油（LU）、燃油涨超4%</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ECI TECH（08013）发布截至2026年2月28日止6个月的中期业绩，该集团取得收益1.21亿港元，同比增加21.64%；期内溢利657万港元，同比增加44.65%；每股基本盈利0.411港</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>46135.37101851852</v>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>2026-04-30 09:00:38</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026年4月30日，早盘开盘，国内期货主力合约涨多跌少，低硫燃料油（LU）、燃油涨超4%，SC原油、碳酸锂涨超2%，焦煤、液化石油气（LPG）、合成橡胶、集运欧线涨近2%。</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-30/doc-inhwftwn6261341.shtml</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmvzk8800445.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>雅居乐集团附属拟9500万元出售浙江祥雅房地产开发50%股权</t>
+          <t>标普：保险公司能够抵御私募信贷崩盘</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>雅居乐集团（03383）发布公告，于2026年4月22日，卖方（公司的间接非全资附属公司南通雅信企业管理咨询有限公司）拟向买方（中国房地产开发集团南通有限公司）出售项目公司...</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="n">
-        <v>46135.37099537037</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>2026-04-30 08:49:04</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>标普全球评级（S&amp;amp;P Global Ratings）对人寿保险公司的私募信贷敞口进行了压力测试，结果令人鼓舞。该公司表示，人寿保险公司具有“韧性”，并已做好充分准备...</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwftwe7452778.shtml</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmvzk8800418.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>美中嘉和与妙佑医疗国际正式签署新合作协议</t>
+          <t>受人工智能支出及法律审查担忧影响 Meta股价下跌</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>美中嘉和（02453）发布公告，近期，公司与妙佑医学教育和研究基金会（Mayo Foundation for Medical Education and Research）（妙佑医疗国际）正式签署新合</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="n">
-        <v>46135.37096064815</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>2026-04-30 08:43:27</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Meta Platforms 周三上调了年度资本支出预测，这表明该公司计划向人工智能基础设施投入数十亿美元，尽管其正面临全球青少年抵制社交媒体可能带来的损失。</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwftwe7449020.shtml</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmvzk8800407.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>基石药业-B根据配售协议发行1.18亿股新股份</t>
+          <t>华勤技术第一季度归母净利润10.61亿元 同比增长25.96%</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>基石药业-B（02616）发布公告，根据2026年4月14日的配售协议于2026年4月22日以一般授权配发及发行1.18亿股新股份。</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="n">
-        <v>46135.37091435185</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>2026-04-30 08:40:27</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 华勤技术（03296）发布2026年第一季度报告，营业收入人民币407.46亿元，同比增长16.42%；归母净利润10.61亿元，同比增长25.96%；基本每股收益1.04元。</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-30/doc-inhwftwi0386476.shtml</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmvzn5577581.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>哈塞特支持鲍威尔关于“临时留任”美联储主席的法律解读</t>
+          <t>高盛：美元/日元若快速升至163-164 或加剧日本干预风险</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 白宫国家经济委员会主任凯文·哈塞特表示支持美联储主席杰罗姆·鲍威尔的计划，即如果下个月鲍威尔任期届满时参议院尚未确认其继任者，他将暂时继续执掌这家央行。</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="n">
-        <v>46135.36946759259</v>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>2026-04-30 08:40:22</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>高盛表示，如果美元/日元迅速上涨至163-164水平，直接干预的可能性可能会增加。策略师Karen Reichgott Fishman在报告中写道，如果日本国债波动性再次飙升...</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwftwe7446832.shtml</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzq3860312.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>韩国股市Kospi指数创下纪录新高 三星电子和SK海力士股价大涨</t>
+          <t>乐动机器人于4月30日至5月6日招股 预计5月11日上市</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>韩国Kospi指数一度上涨2.1%，创下纪录新高，受隔夜美股上涨提振，并且SK海力士盘前报告第一季度营业利润大增四倍。三星电子对指数涨幅贡献最大，股价一度上涨4.8%...</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="n">
-        <v>46135.36565972222</v>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>2026-04-30 08:39:22</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>乐动机器人（01236）于2026年4月30日至5月6日招股，该公司拟全球发售3333.34万股，其中香港发售占10%，国际发售占90%，另有15%超额配股权...</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/ggipo/2026-04-30/doc-inhwftwi0385857.shtml</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzn5574226.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>微软承诺斥资180亿美元建设澳大利亚人工智能产业能力</t>
+          <t>敏实集团将于7月21日派发末期股息每股0.764港元</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 微软公司宣布其史上最大规模的澳大利亚投资计划，承诺到2029年底前投入250亿澳元（折合179亿美元），进一步深耕亚太地区人工智能市场。</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="n">
-        <v>46135.365</v>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>2026-04-30 08:37:50</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>敏实集团（00425）发布公告，该公司将于2026年7月21日派发末期股息每股0.764港元。</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-30/doc-inhwftwi0384763.shtml</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzh5058177.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>油价上涨、欧美股指期货下跌 伊朗和平前景仍不明朗</t>
+          <t>中国重汽将于9月11日派发末期股息每股0.88港元</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>由于伊朗战争解决前景不明朗，油价上涨，美国和欧洲股指期货下跌。标普500指数期货下跌0.3%，此前一度下跌0.9%；纳斯达克100指数期货下跌0.2%...</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="n">
-        <v>46135.3618287037</v>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>2026-04-30 08:36:58</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>中国重汽（03808）发布公告，该公司将于2026年9月11日派发末期股息每股0.88港元。</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-30/doc-inhwftwi0384037.shtml</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzk8794670.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>股海导航_2026年4月23日_沪深股市公告与交易提示</t>
+          <t>江苏宁沪高速公路拟出资5亿元参与紫金信托增资</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>【停牌】 002977 天箭科技 300295 三六五网 601003 柳钢股份 600889 南京化纤 【复牌】 605336 *ST帅电 000609 *ST中迪 【品大事】 中际旭创：2025年</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="n">
-        <v>46135.3605787037</v>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>2026-04-30 08:36:04</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>江苏宁沪高速公路（00177）发布公告，为保障公司在紫金信托有限责任公司（以下简称“紫金信托”）的股东地位与权益，优化资产配置，维护公司投资价值...</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-30/doc-inhwftwi0383359.shtml</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/s/2026-04-23/doc-inhvmvzh5056844.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>马斯克将斥资30亿美元建研究型芯片工厂 其芯片项目拟采用英特尔技术</t>
+          <t>江苏宁沪高速公路拟续聘毕马威华振会计师事务所</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>特斯拉首席执行官埃隆·马斯克表示，公司计划斥资约30亿美元在德克萨斯州建设一座研究型芯片工厂。 马斯克周三在公司季度业绩电话会上表示...</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="n">
-        <v>46135.36024305555</v>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>2026-04-30 08:35:19</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>江苏宁沪高速公路（00177）发布公告，江苏宁沪高速公路股份有限公司（以下简称“本公司”）于2026年4月29 日召开本公司第十一届董事会第二十一次会议审议通过了《关于聘任会...</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-30/doc-inhwftwk7159976.shtml</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzh5054751.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>中科集团控股：股份合并将于4月24日生效</t>
+          <t>江苏宁沪高速公路将于7月13日派发末期股息每股0.49元</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>中科集团控股（03321）发布公告，待联交所授予上市批准后，股份合并将于2026年4月24日生效。合并股份将于2026年4月24日上午九时正开始买卖。</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="n">
-        <v>46135.35865740741</v>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>2026-04-30 08:34:38</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>江苏宁沪高速公路（00177）发布公告，该公司将于2026年7月13日派发末期股息每股0.49元。</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-30/doc-inhwftwn6242511.shtml</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmvzn5569748.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>软银寻求以OpenAI股份为抵押，申请100亿美元保证金贷款</t>
+          <t>江苏宁沪高速公路第一季度归母净利润13.66亿元 同比增长12.81%</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>据知情人士透露，软银集团正以其持有的美国人工智能巨头OpenAI股份作为抵押，申请一笔100亿美元的贷款，以此举进一步加码布局人工智能领域。</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="n">
-        <v>46135.35834490741</v>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>2026-04-30 08:33:59</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 江苏宁沪高速公路（00177）发布2026年第一季度报告，营业收入人民币45.28亿元，同比减少5.31%；归母净利润13.66亿元，同比增长12.81%；基本每股收益0.2711元。</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-30/doc-inhwftwn6242131.shtml</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzk8792280.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>【农产品早评】生猪：宏观氛围偏强，期现走势分歧</t>
+          <t>富卫集团第一季度新增业务销售额按年化新保费计算同比上升4%至7.2亿美元</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>文章来源：混沌天成研究 农产品早评 | 2026年4月23日 品种：油脂油料、橡胶、生猪、苹果、棉花、白糖、红枣 油 脂 棕榈油： 昨日棕榈油主力收盘9822元/吨，上涨199元/吨...</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="n">
-        <v>46135.35745370371</v>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>2026-04-30 08:33:10</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>富卫集团（01828）发布截至2026年3月31日止3个月的首季度新业务摘要，新增业务销售额按年化新保费计算较2025年同期上升4%至7.2亿美元。</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-30/doc-inhwftwn6241685.shtml</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzq3866918.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>【能化早评】美伊进入僵持阶段，封锁预期延长促原油反弹</t>
+          <t>信达生物第一季度产品收入超38亿元 同比增长超过50%</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>文章来源：混沌天成研究 能化早评 | 2026年4月23日 品种：原油、PTA/MEG、甲醇、硅链 原油 供应端：目前主要因素仍在于美伊边打边谈的节奏和霍尔木兹海峡的开放进程...</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="n">
-        <v>46135.35745370371</v>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>2026-04-30 08:31:01</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>信达生物（01801）发布公告，于2026年第一季度，公司产品收入录得超过人民币38亿元，同比增长超过50%，此强劲势头印证了公司“双轮驱动”策略的成功执行。</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-30/doc-inhwftwn6240286.shtml</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzk8803470.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>【黑色早评】节前下游补库，双焦出货持续好转</t>
+          <t>英矽智能公布认购理财产品</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>文章来源：混沌天成研究 黑色早评 | 2026年4月23日 品种：铁矿石、双焦 、钢材、玻璃纯碱  铁矿石 铁矿 一、市场点评 供应端，近期全球铁矿发运有部分回落...</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="n">
-        <v>46135.35745370371</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>2026-04-30 08:29:44</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>英矽智能（03696）发布公告，于2026年4月29日，公司及英硅智能香港（公司的全资附属公司）下达订单认购以下理财产品： （i） 公司下达订单认购由招银国际资产管理有限公司...</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/wm/2026-04-30/doc-inhwftwe7440427.shtml</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzn5582997.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>新疆新鑫矿业将派发末期股息每股0.05元</t>
+          <t>交银国际：中金公司维持“买入”评级 目标价升至26港元</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>新疆新鑫矿业（03833）发布公告，将派发截至2025年12月31日止年度的末期股息每股0.05元。</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="n">
-        <v>46135.3525</v>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>2026-04-30 08:26:51</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>交银国际发布研报称，中金公司（03908）2025年净利润97.91亿元人民币（下同），同比大增71.9%，ROA跃升至9.39%，行业龙头地位进一步巩固...</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/hkgg/2026-04-30/doc-inhwftwn6237884.shtml</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmvzn5564479.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>日经225指数首次突破60,000点大关</t>
+          <t>里昂：中国平安维持“跑赢大市”评级 目标价升至74港元</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 日本日经225指数首次突破60，000点大关，此前受强劲的企业盈利和美国总统特朗普有关与伊朗的停火协议将无限期维持的说法提振，华尔街股市升至历史新高。</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="n">
-        <v>46135.346875</v>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>2026-04-30 08:25:09</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>里昂发布研报称，维持对中国平安（02318）H股“跑赢大市”评级，目标价由71港元上调至74港元；中国平安（601318.SH）A股目标价由77元人民币上调至78元人民币...</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/hkgg/2026-04-30/doc-inhwftwn6236714.shtml</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzq3840342.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>快讯：美股股指期货、现货金银跳水，国际原油快速拉升，WTI原油涨幅扩大至4%</t>
+          <t>巴西央行再次降息25个基点 并维持未来调整政策可能性</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>美股股指期货、现货金银跳水，国际原油快速拉升，WTI原油涨幅扩大至4%。</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="n">
-        <v>46135.34518518519</v>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>2026-04-30 08:24:30</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>巴西央行周三连续第二次会议将利率下调25个基点，同时对未来政策调整持开放态度，评估中东冲突对经济的影响。巴西央行决策委员会（Copom）一致投票决定将指标利率Selic下调...</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwftwe7437173.shtml</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/future/fmnews/2026-04-23/doc-inhvmvzk8782057.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>圣贝拉集团：受托人根据股份奖励计划购买合共14.75万股</t>
+          <t>小摩：中国平安维持“增持”评级 目标价为90港元</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>圣贝拉集团（02508）发布公告，于2026年4月22日，受托人根据圣贝拉2025年股份奖励计划在市场上购买合共14.75万股股份，平均交易价约为每股股份4.22港元，交易总额约为62...</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="n">
-        <v>46135.34283564815</v>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>2026-04-30 08:23:39</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>摩根大通发布研报称，维持中国平安（02318）“增持”评级，目标价为90港元。该行认为，以2027财年预测7倍市盈率及6%的股息率计算，估值仍属合理。</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/hkgg/2026-04-30/doc-inhwftwe7436691.shtml</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmvzn5557380.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>日韩股市均创新高 日经225指数首次突破60000点大关</t>
+          <t>美银证券：长城汽车维持“中性”评级 目标价降至14.3港元</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>日本日经225指数首次突破60000点关口，续创新高。韩国综合股价指数（KOSPI）涨幅超1%，创下历史新高。</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="n">
-        <v>46135.34265046296</v>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>2026-04-30 08:21:36</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>美银证券发布研报称，将长城汽车（02333）2026至2028年的盈利预测分别下调4%、4%及3%，将H股目标价由14.6港元下调至14.3港元，维持“中性”评级...</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/hkgg/2026-04-30/doc-inhwftwe7435463.shtml</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzh5039545.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>华勤技术：香港公开发售获531.33倍认购 每股发售价77.7港元</t>
+          <t>保利物业遭Pandanus Associates Inc.减持41.56万股 每股作价31.2374港元</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>华勤技术（03296）公布配发结果，公司全球发售5854.82万股H股，香港公开发售占10%，国际发售占90%。每股发售价77.7港元，全球发售净筹约44.63亿港元。</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="n">
-        <v>46135.34231481481</v>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>2026-04-30 08:20:15</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>香港联交所最新数据显示，4月24日，Pandanus Associates Inc．减持保利物业（06049）41.56万股，每股作价31.2374港元，总金额约为1298.23万港元。</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/wm/2026-04-30/doc-inhwftwe7434729.shtml</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggipo/2026-04-23/doc-inhvmvzk8779575.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>韩国将从下月起扩大液化石油气减税幅度，以减轻燃料成本负担</t>
+          <t>小摩：招商银行维持“增持”评级 目标价62港元</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 韩国政府周四宣布，将从下个月开始将液化石油气（LPG）丁烷产品的燃油税减税幅度提高一倍以上，以减轻消费者的成本负担。</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="n">
-        <v>46135.33975694444</v>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>2026-04-30 08:19:32</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>摩根大通发布研报称，招商银行（03968）净利息收入复苏及财富管理强劲动能未能转化为强劲利润增长，且已较同业估值存在溢价。在管理层未有就增长前景或总回报作出明确承诺...</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/hkgg/2026-04-30/doc-inhwftwk7147329.shtml</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzh5037351.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>思派健康附属拟5173万元出售思派致合科技(广州)100%股权</t>
+          <t>美国据悉寻求没收在海上扣押的与伊朗有关油轮</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>思派健康（00314）发布公告，于2026年4月22日，思派投资（公司全资附属公司）（作为卖方）与大参林（作为买方）订立股权转让协议。</t>
-        </is>
-      </c>
-      <c r="C87" s="1" t="n">
-        <v>46135.33625</v>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>2026-04-30 08:18:35</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>一位白宫高级官员透露，美国政府正寻求没收两艘与伊朗有关的油轮，对伊朗实施封锁的美国海军扣押了这两艘油轮。 这位官员表示，美国司法部已启动没收程序...</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwfpqn7277777.shtml</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/wm/2026-04-23/doc-inhvmvzq3832912.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>金力永磁第一季度归母净利润1.93亿元 同比增长20.09%</t>
+          <t>里昂：招商银行首季业绩好坏参半 财管收入及净息差胜预期</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>金力永磁（06680）发布2026年第一季度业绩快报，公司实现营业收入人民币20.36亿元，同比增长16.05%，实现归属于上市公司股东的净利润人民币1.93亿元，同比增长20.09%...</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="n">
-        <v>46135.33553240741</v>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>2026-04-30 08:18:20</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>里昂发布研报称，招商银行（03968）第一季业绩好坏参半，财富管理收入及净息差胜于预期，但手续费及资本表现疲弱。期内，经营收入同比增长3.5%，拨备前营运利润增长4.2%...</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/hkgg/2026-04-30/doc-inhwfpqh7564864.shtml</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmvzq3832098.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>日韩股市集体高开 日股升至纪录新高</t>
+          <t>大摩：招商银行给予“增持”评级 目标价为63.4港元</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 日经225指数上午开盘报59758.64点，涨幅0.29%。日本股市日经指数升至纪录新高。韩国综合股价指数（KOSPI）开盘上涨1.1%，至6488.83点。</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="n">
-        <v>46135.33461805555</v>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>2026-04-30 08:17:19</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>摩根士丹利发布研报称，招商银行（03968）今年首季收入及盈利录得平稳增长。期内，营业收入同比上升3.8%，主要受惠于净利息收入年增5%...</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/hkgg/2026-04-30/doc-inhwfpqn7277297.shtml</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzq3831079.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>先声药业：已主动撤回乐德奇拜单抗的NDA 并预计本月重新递交NDA</t>
+          <t>美联储决策凸显分歧 分析师称亚洲货币和债券料将承压</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>先声药业（02096）发布公告，本集团与香港康乃德生物医药有限公司合作的创新药乐德奇拜单抗新药上市申请（NDA）获国家药品监督管理局（NMPA）受理...</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="n">
-        <v>46135.33458333334</v>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>2026-04-30 08:16:27</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>分析人士称，美联储维持利率不变，但一些决策者持鹰派异议，这使得亚洲债券和货币可能会下跌。 他们补充说，油价突破每桶120美元预计也会对韩国...</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwfpqm0499697.shtml</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmvzq3831045.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>三星电子3.7万工人将举行集会，为下月罢工做准备</t>
+          <t>高盛：招商银行维持“买入”评级 目标价52.86港元</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>三星电子工会表示，他们预计周四将有约 37000 名工人参加在韩国举行的集会，下个月将举行罢工。 这次集会将于三星位于平泽市的巨型芯片工厂举行...</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="n">
-        <v>46135.33423611111</v>
-      </c>
-      <c r="D91" t="inlineStr"/>
+          <t>2026-04-30 08:15:56</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>高盛发布研报称，招商银行（03968）首季拨备前利润及纯利分别较该行预期低3%及5%，表现逊预期主要由于手续费收入增长放缓、投资收益同比下跌7%，以及净息差持续收窄。</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/hkgg/2026-04-30/doc-inhwfpqm0499426.shtml</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzq3830674.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>江苏宁沪高速公路拟向丹金公司增资1.28亿元</t>
+          <t>韩国3月份工业产出和零售销售均实现环比增长</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>江苏宁沪高速公路（00177）发布公告，2026年4月22日，公司与常州交控、中交第三航务工程局有限公司、江苏路翔交通工程有限公司、无锡交通建设工程集团股份有限公司...</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="n">
-        <v>46135.33400462963</v>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>2026-04-30 08:15:37</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>周四公布的官方数据显示，韩国3月份工业产出、零售销售和设施投资均实现环比增长，这是自去年9月以来的首次。 韩国数据和统计部的数据显示，上月工业产出小幅增长0.3%...</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwfpqm0499293.shtml</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmvzn5545898.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>力天影业于4月22日完成发行6800万股新股</t>
+          <t>交银国际：海尔智家维持“买入”评级 目标价30.1港元</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>力天影业（09958）公布，2026年4月22日完成发行6800万股新股，每股发行价0.156港元。</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="n">
-        <v>46135.33321759259</v>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>2026-04-30 08:14:55</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>交银国际发布研报称，海尔智家（06690）首季业绩阶段性承压，后续有望逐季改善。首季公司营业收入/扣非净利润同比下降6.9%及17.2%，至各736.9亿元及44...</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/hkgg/2026-04-30/doc-inhwfpqh7563388.shtml</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmvzk8767643.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>新明中国建议按“25并1”基准实施股份合并</t>
+          <t>找钢集团-W遭MPC II L.P.减持32.4万股 每股作价1港元</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>新明中国（02699）公布，作为2026年供股的先决条件，公司建议按每25股每股面值0.01港元的现有股份合并为1股每股面值0.25港元的合并股份的基准实施股份合并。</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="n">
-        <v>46135.33266203704</v>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>2026-04-30 08:10:43</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>香港联交所最新资料显示，4月27日，MPC II L.P．减持找钢集团-W（06676）32.4万股，每股作价1港元，总金额为32.4万港元。减持后最新持股数目约为6147.20万股...</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-30/doc-inhwfpqq6360053.shtml</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmvzk8766738.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>日本反对韩国 MBK Partners 收购牧野铣床制作所</t>
+          <t>三星电子第一季度利润激增八倍 创历史新高</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>日本牧野铣床制作所发布公告称，出于国家安全方面的考量，日本政府已要求总部位于首尔的私募股权公司 MBK 伙伴基金取消其原定的本次收购计划。</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="n">
-        <v>46135.33210648148</v>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>2026-04-30 08:10:24</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>三星电子周四表示，得益于人工智能热潮引发的供应短缺，芯片价格随之走高，推动其第一季度营业利润飙升八倍，创历史新高。这家全球最大的内存芯片制造商在1月至3月期间实现...</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwfpqn7273506.shtml</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-23/doc-inhvmvzk8765737.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>赛力斯拟回购10亿至20亿元的A股 助力价值回归</t>
+          <t>凯莱英遭Norges Bank减持18.49万股 每股作价约102.86港元</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>赛力斯（09927）公布，基于对公司未来发展前景的信心和对公司价值的高度认可，践行以“投资者为本”的发展理念，维护公司和股东利益，增强投资者信心...</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="n">
-        <v>46135.33208333333</v>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>2026-04-30 08:09:45</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>香港联交所最新资料显示，4月27日，Norges Bank减持凯莱英（06821）18.49万股，每股作价102.8593港元，总金额约为1901.87万港元。</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-30/doc-inhwfpqq6359515.shtml</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmvzn5542904.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>金沙中国有限公司第一季度净收入同比增加45.5%至2.94亿美元</t>
+          <t>中创智领遭贝莱德减持4.3万股 每股作价18.5819港元</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>金沙中国有限公司（01928）公布，根据美国公认会计原则，金沙中国2026年第一季的净收益总额同比增加23.6%至21亿美元；净收入同比增加45.5%至2.94亿美元。</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="n">
-        <v>46135.33145833333</v>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t>2026-04-30 08:09:00</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>香港联交所最新数据显示，4月23日，贝莱德减持中创智领（00564）4.3万股，每股作价18.5819港元，总金额约为79.90万港元。减持后最新持股数目为1698.42万股...</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-30/doc-inhwfpqn7272616.shtml</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmvzh5029045.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>联想控股：联泓新科第一季度归母净利润约1.45亿元 同比增长102.67%</t>
+          <t>快意智能获廖维滔增持5000万股 每股作价0.36港元</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>联想控股（03396）发布公告，联泓新科（003022.SZ）于2026年第一季度实现营业收入约22.46亿元，同比增长45.93%；归属于上市公司股东的净利润约1.45亿元，同比增长102...</t>
-        </is>
-      </c>
-      <c r="C98" s="1" t="n">
-        <v>46135.33010416666</v>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>2026-04-30 08:06:44</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>香港联交所最新资料显示，4月22日，廖维滔增持快意智能（08040）5000万股，每股作价0.36港元，总金额为1800万港元。增持后最新持股数目为6502万股，最新持股比例为19.12%。</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-30/doc-inhwfpqn7270537.shtml</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmrts3956763.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>远大医药获董事会主席唐纬坤增持5万股 每股作价约6.47港元</t>
+          <t>利时集团控股获Wonder Force Holdings Limited增持8亿股 每股作价0.0761港元</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>香港联交所最新数据显示，4月22日，董事会主席唐纬坤增持远大医药（00512）5万股，每股作价6.472港元，总金额为32.36万港元。增持后最新持股数目为111万股...</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="n">
-        <v>46135.32912037037</v>
-      </c>
-      <c r="D99" t="inlineStr"/>
+          <t>2026-04-30 08:05:53</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>联交所最新资料显示，4月24日，Wonder Force Holdings Limited增持利时集团控股（00526）8亿股，每股作价0.0761港元，涉及总金额为6088万港元。</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-30/doc-inhwfpqq6356514.shtml</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-23/doc-inhvmrtk5157488.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>旭日企业获董事长杨振鑫增持4.4万股 每股作价1.41港元</t>
+          <t>中国生物制药获副主席郑翔玲增持100万股 每股作价约5.47港元</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>香港联交所最新数据显示，4月21日，董事长杨振鑫增持旭日企业（00393）4.4万股，每股作价1.41港元，总金额约为6.20万港元。增持后最新持股数目约为9.59亿股...</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="n">
-        <v>46135.32844907408</v>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>2026-04-30 08:04:55</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>香港联交所最新数据显示，4月29日，副主席郑翔玲增持中国生物制药（01177）100万股，每股作价5.4705港元，总金额为547.05万港元。</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/hkstock/ggscyd/2026-04-30/doc-inhwfpqn7268988.shtml</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/wm/2026-04-23/doc-inhvmrtq5669693.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>黄金交易提醒：伊朗霍尔木兹“扣船”+特朗普“假停火”，金价反弹受阻后剑指4400？</t>
+          <t>美国提议建立新联盟 以恢复霍尔木兹海峡的航运</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>文章来源：汇通财经 现货黄金周三（4月22日）反弹受阻。尽管特朗普单方面宣布延长停火期限，且有消息称美国可能开放对伊朗的封锁，市场一度燃起乐观情绪...</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="n">
-        <v>46135.32708333333</v>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>2026-04-30 08:03:07</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>据媒体引述周二发给美国驻外使馆的国务院内部电报报道，作为力图恢复霍尔木兹海峡航运的最新举措，特朗普政府正在邀请其他国家加入一个新的国际联盟...</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-04-30/doc-inhwfpqq6353730.shtml</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/money/nmetal/hjzx/2026-04-23/doc-inhvmrtk5156972.shtml</t>
+          <t>新浪新闻</t>
         </is>
       </c>
     </row>
